--- a/sample_data/事件评论信息_示例.xlsx
+++ b/sample_data/事件评论信息_示例.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,1026 +430,1032 @@
   </sheetPr>
   <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>评论者</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>点赞数</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>wode公主殿下</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>中国队加油🇨🇳🇨🇳</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>小绿宝石beryl</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>中国队加油，放平心态全力冲！[打call][打call][打call]</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>戎耀今生</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>盛李豪+张常鸿出10米气步枪，今天射击这块金牌基本可以提前写进账本。</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="2" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>我超想做个超级大锦鲤ya</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>加油[打call]</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>wode猪猪公主</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>中国队加油！🇨🇳🇨🇳🇨🇳</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Starchen1021</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>中国队冲呀🇨🇳[拳頭]</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>未发作业</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>中国石化扬子石化有限公司2026.5.29至6.24间发生多起致死安全生产事故，瞒报部分事故和伤亡人数</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="D8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>戎光砺行</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>中国队加油[微风][心]</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
+      <c r="D9" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>LUFU_</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>期待中国队夺得更多的金牌，为中国亚运健儿助威，加油！加油！加油！</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>哭泣的大饼爱墨墨</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>哇哦，又是看点满满，射击、游泳都超爱</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
+      <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>小猪贩星星</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>中国队加油🇨🇳</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>福鹭大王Re</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>霓凰2017</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>中国队加油[锦鲤附体][努力]</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>-别碰我哥妹</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="D15" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>旦棣</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>中国队加油！！👏🏻👏🏻</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>回眸相似笑-wyb</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>中国队冲鸭</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Lucas-果果</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
+      <c r="D18" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>素锦流年96</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>中国队加油🇨🇳[拳头][拳头]</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
+      <c r="D19" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>偷看童童</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>天使就是angela颖颖</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
+      <c r="D21" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>0452疯婆子</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>中国队🇨🇳加油[打call][打call]</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
+      <c r="D22" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>小财迷呀Nice</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>中国健儿加油[打call][打call][打call][打call][打call]</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
+      <c r="D23" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>张张来了的呀</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>加油加油</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>张张来了的呀</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>中国队冲鸭</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Yi碟阳光</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>中国队加油[鲜花]</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Feiiii_0709</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>中国队加油[打call]</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>一口地瓜</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>中国队加油！！</t>
         </is>
       </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>x玖少年团肖俊DAYTOY</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>🇨🇳🇨🇳🇨🇳💪💪💪。</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>遇见半夏温暖</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>看一下女排半决赛</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>星匠星辰大海</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>点赞中国运动健儿[赞][赞]</t>
         </is>
       </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>文明天天向上</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>中国队加油[赞][赞][赞]</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>思十加二</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>阳春白雪O712</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>中国🇨🇳队加油[拳头][拳头][拳头]</t>
         </is>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>笑笑郝然</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>中国队🇨🇳加油</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>少许小雨愿</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="29" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>你已深埋我心底</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>今日亚运看点满满，18金待决。射击双线冲金，体操男团全力出击，女排半决赛对阵泰国关键一战，女足、女篮齐登场。从清晨铁人到傍晚手球，全天精彩不断。为中国健儿加油，期待捷报频传！</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+      <c r="D37" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>小猫头发又乱啦k_</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
+      <c r="D38" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>我豚兔了orz</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
+      <c r="D39" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>鲍伯阿呆</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>中国队[心]加油</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
+      <c r="D40" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>宁宁Li宁</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
+      <c r="D41" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>小杜映彤心</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
+      <c r="D42" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>SleepdT-Tb</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
+      <c r="D43" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>熊猫Penny-</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>中国队加油！</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
+      <c r="D44" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>情意正农</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
+      <c r="D45" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>呜莓</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
+      <c r="D46" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>LLOUD_Peiiz_bes曦-</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
+      <c r="D47" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>傲娇璐wll</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>中国队加油</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
+      <c r="D48" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>琴蕾合鸣</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>中国队加油🇨🇳</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
+      <c r="D49" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="29" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>-每天都想睡觉de小余Yu-R</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>中国队加油！🇨🇳</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
+      <c r="D50" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>琳雬烟笙云娇</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>中国队加油！🇨🇳🇨🇳🇨🇳</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="2" t="n">
         <v>0</v>
       </c>
     </row>
